--- a/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B2FDFB-E046-4774-8B98-F68381B38EE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="12696"/>
+    <workbookView xWindow="204" yWindow="2376" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -99,12 +100,15 @@
   </si>
   <si>
     <t>Delivery Type ID</t>
+  </si>
+  <si>
+    <t>Order Date  (YYYY-MM-DD)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -450,8 +454,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -463,24 +467,25 @@
     <col min="7" max="8" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.21875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -512,48 +517,51 @@
         <v>3</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B2FDFB-E046-4774-8B98-F68381B38EE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A53E270-CF1E-42C8-A241-1A64B249B486}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="204" yWindow="2376" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -103,6 +103,21 @@
   </si>
   <si>
     <t>Order Date  (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 1</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 2</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 3</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 4</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 5</t>
   </si>
 </sst>
 </file>
@@ -455,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -483,9 +498,10 @@
     <col min="24" max="24" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -563,6 +579,21 @@
       </c>
       <c r="Z1" s="1" t="s">
         <v>23</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A53E270-CF1E-42C8-A241-1A64B249B486}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D17529-7833-4445-8E28-79AB2B0EFF3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>Shipper Reference Number 5</t>
+  </si>
+  <si>
+    <t>Open Shipment</t>
   </si>
 </sst>
 </file>
@@ -470,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -501,7 +504,7 @@
     <col min="27" max="31" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -594,6 +597,9 @@
       </c>
       <c r="AE1" t="s">
         <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D17529-7833-4445-8E28-79AB2B0EFF3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80914589-FB6B-4E84-8C58-D3D21F2A3C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>Open Shipment</t>
+  </si>
+  <si>
+    <t>Return Address ID</t>
   </si>
 </sst>
 </file>
@@ -473,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -504,7 +507,7 @@
     <col min="27" max="31" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -600,6 +603,9 @@
       </c>
       <c r="AF1" t="s">
         <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80914589-FB6B-4E84-8C58-D3D21F2A3C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90391063-40B4-4D6F-8E33-15583BE20251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>Open Shipment</t>
-  </si>
-  <si>
-    <t>Return Address ID</t>
   </si>
 </sst>
 </file>
@@ -476,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -507,7 +504,7 @@
     <col min="27" max="31" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -603,9 +600,6 @@
       </c>
       <c r="AF1" t="s">
         <v>31</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90391063-40B4-4D6F-8E33-15583BE20251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D17529-7833-4445-8E28-79AB2B0EFF3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D17529-7833-4445-8E28-79AB2B0EFF3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6361545-CBB2-4743-8900-AF08BE0F26AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>Open Shipment</t>
+  </si>
+  <si>
+    <t>Parcel Value</t>
   </si>
 </sst>
 </file>
@@ -473,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -504,7 +507,7 @@
     <col min="27" max="31" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -600,6 +603,9 @@
       </c>
       <c r="AF1" t="s">
         <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6361545-CBB2-4743-8900-AF08BE0F26AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0813DC-65D5-4EAC-A272-95DE4956E5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -505,6 +505,7 @@
     <col min="25" max="25" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="31" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.3">
@@ -604,7 +605,7 @@
       <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
     </row>

--- a/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0813DC-65D5-4EAC-A272-95DE4956E5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -124,12 +123,18 @@
   </si>
   <si>
     <t>Parcel Value</t>
+  </si>
+  <si>
+    <t>Consignee Address Latitude</t>
+  </si>
+  <si>
+    <t>Consignee Address Longitude</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -475,8 +480,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -487,28 +492,29 @@
     <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="31" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.88671875" style="1"/>
+    <col min="10" max="11" width="21.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.21875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="33" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -537,75 +543,81 @@
         <v>2</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>32</v>
       </c>
     </row>

--- a/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Replacement Shipment Template.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -129,6 +129,12 @@
   </si>
   <si>
     <t>Consignee Address Longitude</t>
+  </si>
+  <si>
+    <t>Retail Pickup Store ID</t>
+  </si>
+  <si>
+    <t>Retail Deliver Store ID</t>
   </si>
 </sst>
 </file>
@@ -481,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -511,10 +517,12 @@
     <col min="27" max="27" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="33" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.88671875" style="1"/>
+    <col min="35" max="35" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -619,6 +627,12 @@
       </c>
       <c r="AI1" s="1" t="s">
         <v>32</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
